--- a/output/第10期計画_9月作業_アンケート分析の作業状況.xlsx
+++ b/output/第10期計画_9月作業_アンケート分析の作業状況.xlsx
@@ -1512,7 +1512,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月4日受領。施設等票18件・定員652人・入所者536人。新規入所335人・退去349人の入所前／退去先を集計済み。北海道の名簿により区域内の母数を26施設と確定した。</t>
+          <t>令和8年8月4日受領。施設等票18件・定員652人・入所者536人。新規入所335人・退去349人の入所前／退去先を集計済み。北海道の名簿により区域内の母数を31施設と確定した（指定19＋指定外12。回答18・未回答13）。</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>①②③は配布数の記録がないため回収率を算定していない。公表データによる母数（居宅介護支援13事業所、区域内の施設・住まい26施設、訪問介護13事業所）を用いた把握率を暫定値としている。</t>
+          <t>①②③は配布数の記録がないため回収率を算定していない。公表データによる母数（居宅介護支援13事業所、区域内の施設・住まい31施設、訪問介護13事業所）を用いた把握率を暫定値としている。</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>居所変更実態調査は区域内26施設のうち13施設が未回答であり、うち区域内最大の特定施設（定員100人）を含む。把握率58.1％のまま用いるか、追加照会を行うかを決める。</t>
+          <t>居所変更実態調査は区域内31施設のうち13施設が未回答であり、うち区域内最大の特定施設（定員100人）を含む。把握率58.1％のまま用いるか、追加照会を行うかを決める。</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>把握率58.1％（26施設中18施設）であり、区域内最大の特定施設が未回答である。健康とくらしの調査【大雪－問3】1）2）による補完値5.4％（n=4,446票）を併記する案。</t>
+          <t>把握率58.1％（31施設中18施設）であり、区域内最大の特定施設が未回答である。健康とくらしの調査【大雪－問3】1）2）による補完値5.4％（n=4,446票）を併記する案。</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
